--- a/public/templates/inje-gt-masters_standings_template.xlsx
+++ b/public/templates/inje-gt-masters_standings_template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,15 +418,21 @@
         <v>드라이버</v>
       </c>
       <c r="F1" t="str">
-        <v>결승pt</v>
+        <v>R1</v>
       </c>
       <c r="G1" t="str">
-        <v>완주pt</v>
+        <v>R2</v>
       </c>
       <c r="H1" t="str">
-        <v>예선pt</v>
+        <v>R3</v>
       </c>
       <c r="I1" t="str">
+        <v>R4</v>
+      </c>
+      <c r="J1" t="str">
+        <v>R5</v>
+      </c>
+      <c r="K1" t="str">
         <v>합계</v>
       </c>
     </row>
@@ -447,15 +453,21 @@
         <v>김태환 / 이인용</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>28</v>
       </c>
     </row>
@@ -466,14 +478,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -492,15 +504,21 @@
         <v>팀명</v>
       </c>
       <c r="F1" t="str">
-        <v>결승pt</v>
+        <v>R1</v>
       </c>
       <c r="G1" t="str">
-        <v>완주pt</v>
+        <v>R2</v>
       </c>
       <c r="H1" t="str">
-        <v>예선pt</v>
+        <v>R3</v>
       </c>
       <c r="I1" t="str">
+        <v>R4</v>
+      </c>
+      <c r="J1" t="str">
+        <v>R5</v>
+      </c>
+      <c r="K1" t="str">
         <v>합계</v>
       </c>
     </row>
@@ -521,15 +539,21 @@
         <v>오버리미트</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>28</v>
       </c>
     </row>
@@ -540,14 +564,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -653,103 +677,109 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>결승pt</v>
+        <v>R1</v>
       </c>
       <c r="B7" t="str">
-        <v>필수</v>
+        <v>선택</v>
       </c>
       <c r="C7" t="str">
         <v>정수</v>
       </c>
       <c r="D7" t="str">
-        <v>시즌 누적 결승 포인트 합계</v>
+        <v>라운드 1 획득 포인트 (미참가 시 0 또는 빈칸)</v>
       </c>
       <c r="E7" t="str">
-        <v>25, 43, 68</v>
+        <v>28, 0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>완주pt</v>
+        <v>R2</v>
       </c>
       <c r="B8" t="str">
-        <v>필수</v>
+        <v>선택</v>
       </c>
       <c r="C8" t="str">
         <v>정수</v>
       </c>
       <c r="D8" t="str">
-        <v>시즌 누적 완주 보너스 포인트 합계</v>
+        <v>라운드 2 획득 포인트 (미참가 시 0 또는 빈칸)</v>
       </c>
       <c r="E8" t="str">
-        <v>3, 6, 9</v>
+        <v>25, 0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>예선pt</v>
+        <v>R3</v>
       </c>
       <c r="B9" t="str">
-        <v>필수</v>
+        <v>선택</v>
       </c>
       <c r="C9" t="str">
         <v>정수</v>
       </c>
       <c r="D9" t="str">
-        <v>시즌 누적 예선 포인트 합계</v>
+        <v>라운드 3 획득 포인트 (미참가 시 0 또는 빈칸)</v>
       </c>
       <c r="E9" t="str">
-        <v>0, 1, 3</v>
+        <v>20, 0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>합계</v>
+        <v>R4</v>
       </c>
       <c r="B10" t="str">
-        <v>필수</v>
+        <v>선택</v>
       </c>
       <c r="C10" t="str">
         <v>정수</v>
       </c>
       <c r="D10" t="str">
-        <v>결승pt + 완주pt + 예선pt = 합계 (자동 계산 권장)</v>
+        <v>라운드 4 획득 포인트 (미참가 시 0 또는 빈칸)</v>
       </c>
       <c r="E10" t="str">
-        <v>28, 50, 80</v>
+        <v>18, 0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>R5</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>선택</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>정수</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>라운드 5 획득 포인트 (미참가 시 0 또는 빈칸)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>15, 0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>[검증 규칙]</v>
+        <v>합계</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>필수</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>정수</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>R1+R2+R3+R4+R5 = 합계 (자동 계산 권장)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>28, 50, 80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>합계 = 결승pt + 완주pt + 예선pt 인지 반드시 확인하세요.</v>
+        <v/>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -763,7 +793,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>사이트에는 합계만 노출됩니다. 세부 항목은 관리용입니다.</v>
+        <v>[검증 규칙]</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -772,12 +802,40 @@
         <v/>
       </c>
       <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>합계 = R1+R2+R3+R4+R5 인지 반드시 확인하세요.</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>사이트에는 합계 및 라운드별 점수가 노출됩니다.</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
   </ignoredErrors>
 </worksheet>
 </file>